--- a/Assets/100_Data/XlsxFiles/Ground_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Ground_Data.xlsx
@@ -19,18 +19,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
   <si>
     <t>HP</t>
-  </si>
-  <si>
-    <t>Light_Brown[Light_Brown]</t>
-  </si>
-  <si>
-    <t>Deep_Brown[Deep_Brown]</t>
-  </si>
-  <si>
-    <t>Lava_Earth[Lava_Earth]</t>
   </si>
   <si>
     <t>Id</t>
@@ -75,6 +66,10 @@
   </si>
   <si>
     <t>1001;1003;1005</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ground1</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1022,25 +1017,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
       </c>
       <c r="F1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -1048,7 +1043,7 @@
         <v>5001</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1063,7 +1058,7 @@
         <v>1001</v>
       </c>
       <c r="G2" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -1071,7 +1066,7 @@
         <v>5002</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C3">
         <v>6</v>
@@ -1083,10 +1078,10 @@
         <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1094,7 +1089,7 @@
         <v>5003</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C4">
         <v>11</v>
@@ -1106,10 +1101,10 @@
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1117,7 +1112,7 @@
         <v>5004</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C5">
         <v>16</v>
@@ -1132,7 +1127,7 @@
         <v>1007</v>
       </c>
       <c r="G5" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/100_Data/XlsxFiles/Ground_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Ground_Data.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Drill_Game\Assets\100_Data\XlsxFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koseonghyeon\Desktop\Drill_Game\Drill_game\Assets\100_Data\XlsxFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{389C4B63-D09A-457E-8240-F1AF43522B51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16170" windowHeight="9705"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ground_Data" sheetId="1" r:id="rId1"/>
@@ -76,7 +77,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -726,16 +727,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="표1" displayName="표1" ref="A1:G5" totalsRowShown="0">
-  <autoFilter ref="A1:G5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="A1:G5" totalsRowShown="0">
+  <autoFilter ref="A1:G5" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="7">
-    <tableColumn id="6" name="Id"/>
-    <tableColumn id="7" name="Name"/>
-    <tableColumn id="1" name="StartDepth"/>
-    <tableColumn id="2" name="EndDepth"/>
-    <tableColumn id="3" name="HP"/>
-    <tableColumn id="4" name="DropItems"/>
-    <tableColumn id="5" name="SpriteAddressable"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Id"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Name"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="StartDepth"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="EndDepth"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="HP"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="DropItems"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="SpriteAddressable"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1003,7 +1004,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>

--- a/Assets/100_Data/XlsxFiles/Ground_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Ground_Data.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koseonghyeon\Desktop\Drill_Game\Drill_game\Assets\100_Data\XlsxFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Drill_Game\Assets\100_Data\XlsxFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{389C4B63-D09A-457E-8240-F1AF43522B51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Ground_Data" sheetId="1" r:id="rId1"/>
@@ -20,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="28">
   <si>
     <t>HP</t>
   </si>
@@ -71,13 +70,62 @@
   </si>
   <si>
     <t>Ground1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ground_5</t>
+  </si>
+  <si>
+    <t>Ground_6</t>
+  </si>
+  <si>
+    <t>Ground_7</t>
+  </si>
+  <si>
+    <t>Ground_8</t>
+  </si>
+  <si>
+    <t>Ground_9</t>
+  </si>
+  <si>
+    <t>Ground_10</t>
+  </si>
+  <si>
+    <t>Ground1</t>
+  </si>
+  <si>
+    <t>1003;1005;1007</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1005;1007;1009</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1007;1009;1011</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1009;1011;1013</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1011;1013;1015</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1013;1015;1017</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1015;1017;1019</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -727,16 +775,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="A1:G5" totalsRowShown="0">
-  <autoFilter ref="A1:G5" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="표1" displayName="표1" ref="A1:G11" totalsRowShown="0">
+  <autoFilter ref="A1:G11"/>
   <tableColumns count="7">
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Id"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Name"/>
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="StartDepth"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="EndDepth"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="HP"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="DropItems"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="SpriteAddressable"/>
+    <tableColumn id="6" name="Id"/>
+    <tableColumn id="7" name="Name"/>
+    <tableColumn id="1" name="StartDepth"/>
+    <tableColumn id="2" name="EndDepth"/>
+    <tableColumn id="3" name="HP"/>
+    <tableColumn id="4" name="DropItems"/>
+    <tableColumn id="5" name="SpriteAddressable"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1004,8 +1052,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -1076,7 +1124,7 @@
         <v>10</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F3" t="s">
         <v>11</v>
@@ -1093,13 +1141,13 @@
         <v>5</v>
       </c>
       <c r="C4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4">
         <v>15</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="F4" t="s">
         <v>12</v>
@@ -1116,19 +1164,157 @@
         <v>6</v>
       </c>
       <c r="C5">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>1007</v>
+        <v>500</v>
+      </c>
+      <c r="F5" t="s">
+        <v>21</v>
       </c>
       <c r="G5" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5005</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6">
+        <v>24</v>
+      </c>
+      <c r="D6">
+        <v>25</v>
+      </c>
+      <c r="E6">
+        <v>1000</v>
+      </c>
+      <c r="F6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>5006</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7">
+        <v>30</v>
+      </c>
+      <c r="D7">
+        <v>30</v>
+      </c>
+      <c r="E7">
+        <v>5000</v>
+      </c>
+      <c r="F7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>5007</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8">
+        <v>36</v>
+      </c>
+      <c r="D8">
+        <v>35</v>
+      </c>
+      <c r="E8">
+        <v>10000</v>
+      </c>
+      <c r="F8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>5008</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9">
+        <v>42</v>
+      </c>
+      <c r="D9">
+        <v>40</v>
+      </c>
+      <c r="E9">
+        <v>30000</v>
+      </c>
+      <c r="F9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>5009</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10">
+        <v>48</v>
+      </c>
+      <c r="D10">
+        <v>45</v>
+      </c>
+      <c r="E10">
+        <v>70000</v>
+      </c>
+      <c r="F10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>5010</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11">
+        <v>54</v>
+      </c>
+      <c r="D11">
+        <v>50</v>
+      </c>
+      <c r="E11">
+        <v>100000</v>
+      </c>
+      <c r="F11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/100_Data/XlsxFiles/Ground_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Ground_Data.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="33">
   <si>
     <t>HP</t>
   </si>
@@ -85,12 +85,6 @@
     <t>Ground_8</t>
   </si>
   <si>
-    <t>Ground_9</t>
-  </si>
-  <si>
-    <t>Ground_10</t>
-  </si>
-  <si>
     <t>Ground1</t>
   </si>
   <si>
@@ -110,15 +104,43 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>1011;1013;1015</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>1013;1015;1017</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>1015;1017;1019</t>
+    <t>Color</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>168;159;151</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>255;152;88</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>201;188;180</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>215;204;198</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1011;1013;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>255;184;62</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>98;100;174</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>163;88;218</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>88;218;175</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -775,15 +797,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="표1" displayName="표1" ref="A1:G11" totalsRowShown="0">
-  <autoFilter ref="A1:G11"/>
-  <tableColumns count="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="표1" displayName="표1" ref="A1:H9" totalsRowShown="0">
+  <autoFilter ref="A1:H9"/>
+  <tableColumns count="8">
     <tableColumn id="6" name="Id"/>
     <tableColumn id="7" name="Name"/>
     <tableColumn id="1" name="StartDepth"/>
     <tableColumn id="2" name="EndDepth"/>
     <tableColumn id="3" name="HP"/>
     <tableColumn id="4" name="DropItems"/>
+    <tableColumn id="8" name="Color"/>
     <tableColumn id="5" name="SpriteAddressable"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1053,7 +1076,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -1064,7 +1087,7 @@
     <col min="7" max="7" width="23.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -1084,10 +1107,13 @@
         <v>9</v>
       </c>
       <c r="G1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>5001</v>
       </c>
@@ -1107,10 +1133,13 @@
         <v>1001</v>
       </c>
       <c r="G2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>5002</v>
       </c>
@@ -1130,10 +1159,13 @@
         <v>11</v>
       </c>
       <c r="G3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>5003</v>
       </c>
@@ -1153,10 +1185,13 @@
         <v>12</v>
       </c>
       <c r="G4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>5004</v>
       </c>
@@ -1173,13 +1208,16 @@
         <v>500</v>
       </c>
       <c r="F5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5005</v>
       </c>
@@ -1196,13 +1234,16 @@
         <v>1000</v>
       </c>
       <c r="F6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G6" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="H6" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5006</v>
       </c>
@@ -1219,13 +1260,16 @@
         <v>5000</v>
       </c>
       <c r="F7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G7" t="s">
-        <v>20</v>
+        <v>30</v>
+      </c>
+      <c r="H7" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>5007</v>
       </c>
@@ -1242,13 +1286,16 @@
         <v>10000</v>
       </c>
       <c r="F8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G8" t="s">
-        <v>20</v>
+        <v>31</v>
+      </c>
+      <c r="H8" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>5008</v>
       </c>
@@ -1265,56 +1312,13 @@
         <v>30000</v>
       </c>
       <c r="F9" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>5009</v>
-      </c>
-      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9" t="s">
         <v>18</v>
-      </c>
-      <c r="C10">
-        <v>48</v>
-      </c>
-      <c r="D10">
-        <v>45</v>
-      </c>
-      <c r="E10">
-        <v>70000</v>
-      </c>
-      <c r="F10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>5010</v>
-      </c>
-      <c r="B11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11">
-        <v>54</v>
-      </c>
-      <c r="D11">
-        <v>50</v>
-      </c>
-      <c r="E11">
-        <v>100000</v>
-      </c>
-      <c r="F11" t="s">
-        <v>27</v>
-      </c>
-      <c r="G11" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/100_Data/XlsxFiles/Ground_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Ground_Data.xlsx
@@ -1082,7 +1082,7 @@
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="4" max="4" width="12.75" customWidth="1"/>
-    <col min="5" max="5" width="11.25" customWidth="1"/>
+    <col min="5" max="5" width="27.25" customWidth="1"/>
     <col min="6" max="6" width="33.25" customWidth="1"/>
     <col min="7" max="7" width="23.75" customWidth="1"/>
   </cols>
@@ -1127,7 +1127,7 @@
         <v>5</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>6400</v>
       </c>
       <c r="F2">
         <v>1001</v>
@@ -1153,7 +1153,7 @@
         <v>10</v>
       </c>
       <c r="E3">
-        <v>20</v>
+        <v>25840</v>
       </c>
       <c r="F3" t="s">
         <v>11</v>
@@ -1173,13 +1173,13 @@
         <v>5</v>
       </c>
       <c r="C4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4">
         <v>15</v>
       </c>
       <c r="E4">
-        <v>100</v>
+        <v>194400</v>
       </c>
       <c r="F4" t="s">
         <v>12</v>
@@ -1199,13 +1199,13 @@
         <v>6</v>
       </c>
       <c r="C5">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D5">
         <v>20</v>
       </c>
       <c r="E5">
-        <v>500</v>
+        <v>388800</v>
       </c>
       <c r="F5" t="s">
         <v>19</v>
@@ -1225,13 +1225,13 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D6">
         <v>25</v>
       </c>
       <c r="E6">
-        <v>1000</v>
+        <v>622080</v>
       </c>
       <c r="F6" t="s">
         <v>20</v>
@@ -1251,13 +1251,13 @@
         <v>15</v>
       </c>
       <c r="C7">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D7">
         <v>30</v>
       </c>
       <c r="E7">
-        <v>5000</v>
+        <v>1010880</v>
       </c>
       <c r="F7" t="s">
         <v>21</v>
@@ -1277,13 +1277,13 @@
         <v>16</v>
       </c>
       <c r="C8">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D8">
         <v>35</v>
       </c>
       <c r="E8">
-        <v>10000</v>
+        <v>1632960</v>
       </c>
       <c r="F8" t="s">
         <v>22</v>
@@ -1303,13 +1303,13 @@
         <v>17</v>
       </c>
       <c r="C9">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D9">
         <v>40</v>
       </c>
       <c r="E9">
-        <v>30000</v>
+        <v>1632960</v>
       </c>
       <c r="F9" t="s">
         <v>28</v>
